--- a/2026_09_09/TakeAwayOrder.xlsx
+++ b/2026_09_09/TakeAwayOrder.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026_09\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026_09\2026_09_09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE33A7D-7491-447E-AC90-B5415E9C2501}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F150FF-5A10-4C18-B55D-3DD1598058D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,19 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>total_transaction</t>
-  </si>
-  <si>
-    <t>customer_cancel_number</t>
-  </si>
-  <si>
-    <t>merchant_cancel_number</t>
-  </si>
-  <si>
-    <t>system_cancel_number</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>metric</t>
   </si>
@@ -64,10 +52,19 @@
     <t>merchant_ready_time</t>
   </si>
   <si>
-    <t>p90 meaning:</t>
-  </si>
-  <si>
-    <t>90% orders are accepted/ready within (#) mins.</t>
+    <t>avg calculation</t>
+  </si>
+  <si>
+    <t>remove &gt; 30 mins</t>
+  </si>
+  <si>
+    <t>remove &gt; 60 mins</t>
+  </si>
+  <si>
+    <t>P90:</t>
+  </si>
+  <si>
+    <t>more than 90% order are taken within (#) mins</t>
   </si>
 </sst>
 </file>
@@ -419,16 +416,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -441,105 +432,86 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>167950</v>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>7236</v>
+        <v>153141</v>
       </c>
       <c r="C2">
-        <v>1859</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>5597</v>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E2">
+        <v>0.8</v>
+      </c>
+      <c r="F2">
+        <v>0.62</v>
+      </c>
+      <c r="G2">
+        <v>0.52</v>
+      </c>
+      <c r="H2">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
+      <c r="B3">
+        <v>142824</v>
+      </c>
+      <c r="C3">
+        <v>24.32</v>
+      </c>
+      <c r="D3">
+        <v>16.78</v>
+      </c>
+      <c r="E3">
+        <v>13.37</v>
+      </c>
+      <c r="F3">
+        <v>11.07</v>
+      </c>
+      <c r="G3">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="H3">
+        <v>11.94</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
-        <v>153897</v>
-      </c>
-      <c r="C5">
-        <v>3.1</v>
-      </c>
-      <c r="D5">
-        <v>1.17</v>
-      </c>
-      <c r="E5">
-        <v>0.8</v>
-      </c>
-      <c r="F5">
-        <v>0.62</v>
-      </c>
-      <c r="G5">
-        <v>0.52</v>
-      </c>
-      <c r="H5">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
         <v>13</v>
       </c>
-      <c r="B6">
-        <v>153299</v>
-      </c>
-      <c r="C6">
-        <v>39.99</v>
-      </c>
-      <c r="D6">
-        <v>20.2</v>
-      </c>
-      <c r="E6">
-        <v>14.83</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>9.85</v>
-      </c>
-      <c r="H6">
-        <v>18.97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="K5" t="s">
         <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/2026_09_09/TakeAwayOrder.xlsx
+++ b/2026_09_09/TakeAwayOrder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026_09\2026_09_09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F150FF-5A10-4C18-B55D-3DD1598058D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66FB336-F9AC-4C6C-937C-B2C40D20E756}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>metric</t>
   </si>
@@ -65,6 +65,18 @@
   </si>
   <si>
     <t>more than 90% order are taken within (#) mins</t>
+  </si>
+  <si>
+    <t>total_transaction</t>
+  </si>
+  <si>
+    <t>customer_cancel_number</t>
+  </si>
+  <si>
+    <t>merchant_cancel_number</t>
+  </si>
+  <si>
+    <t>system_cancel_number</t>
   </si>
 </sst>
 </file>
@@ -416,101 +428,129 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>167636</v>
+      </c>
+      <c r="B2">
+        <v>7065</v>
+      </c>
+      <c r="C2">
+        <v>373</v>
+      </c>
+      <c r="D2">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
+      <c r="B7">
         <v>153141</v>
       </c>
-      <c r="C2">
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="D2">
+      <c r="D7">
         <v>1.1499999999999999</v>
       </c>
-      <c r="E2">
+      <c r="E7">
         <v>0.8</v>
       </c>
-      <c r="F2">
+      <c r="F7">
         <v>0.62</v>
       </c>
-      <c r="G2">
+      <c r="G7">
         <v>0.52</v>
       </c>
-      <c r="H2">
+      <c r="H7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
+      <c r="B8">
         <v>142824</v>
       </c>
-      <c r="C3">
+      <c r="C8">
         <v>24.32</v>
       </c>
-      <c r="D3">
+      <c r="D8">
         <v>16.78</v>
       </c>
-      <c r="E3">
+      <c r="E8">
         <v>13.37</v>
       </c>
-      <c r="F3">
+      <c r="F8">
         <v>11.07</v>
       </c>
-      <c r="G3">
+      <c r="G8">
         <v>9.2200000000000006</v>
       </c>
-      <c r="H3">
+      <c r="H8">
         <v>11.94</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J5" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J10" t="s">
         <v>13</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K10" t="s">
         <v>14</v>
       </c>
     </row>
